--- a/exemplo_importacao_alunos.xlsx
+++ b/exemplo_importacao_alunos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="174">
   <si>
     <t xml:space="preserve">nome</t>
   </si>
@@ -97,10 +97,118 @@
     <t xml:space="preserve">horario_aula</t>
   </si>
   <si>
-    <t xml:space="preserve">HEIDER BATISTA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">21 98547-4226</t>
+    <t xml:space="preserve">HELENA RIOS CARVALHO DE BARROS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71 9956-8887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salvador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludmila mãe </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caio Macedo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/03/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:30 às 14:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YASMIN FREIRE PEIXOTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71 99977-7267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice mãe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71 99777267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/03/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/04/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinta-feira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matheus Moreski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mãe Fernanda </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sábado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERICK JENUINO DEBIAZI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54 9267-7276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/09/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRUNA AUEBACH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flávio Silva Almeida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75 9300-8582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/08/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sexta-feira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacqueline Mendes Magalhães</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAPHAEL MARTINUS DE AZEVEDO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 98986-1122</t>
   </si>
   <si>
     <t xml:space="preserve">Rio de Janeiro</t>
@@ -109,115 +217,331 @@
     <t xml:space="preserve">RJ</t>
   </si>
   <si>
-    <t xml:space="preserve">PIX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Affonso Amajones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/05/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sábado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:00 às 15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIRO JULIUS </t>
-  </si>
-  <si>
-    <t xml:space="preserve">31 9140-0292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/05/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIRYEL EUGÊNIO ARNOLD </t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 99603-8867</t>
+    <t xml:space="preserve">20/09/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABRIEL SANCHES SERQUEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/08/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIANA NASCIMENTO CUNHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 99852-6742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/09/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Medina Neves da Silva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 98170-3566</t>
   </si>
   <si>
     <t xml:space="preserve">SP</t>
   </si>
   <si>
-    <t xml:space="preserve">Pablo primo que paga a mensalidade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/06/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAFAEL ALVIM MENDONÇA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 97898-8295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eder pai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 98225-9617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/06/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIOVANE MATHEUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 99231-6969</t>
+    <t xml:space="preserve">01/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCELO KOHLER JUNIOR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">47 9707-5558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVERTON DA SILVA PAZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">51 9697-9573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHIANNA OLIVEIRA CORREA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41 9832-0946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABINADABE NEGRAO PEREIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91 8825-9853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belém</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/01/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIANCA NASCIMENTO CAMPOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 97108-1201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wemmerson Reis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31/05/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO ROBERTO SANTOS DA SILVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 97264-5516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/03/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITORIA MARIA DE PAULA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 99663-6807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELLEN CRISTINA DE SÁ - DRT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 96629-4349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/08/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA CAROLINA UCHA SANTOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 97432-8875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/09/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPERIMENTAL Gabriella dos Santos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00000-0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAURA V DANTAS DOS SANTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 97686-0919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/01/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILVANA BARROS CRESPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 99577-0577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/12/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENZO FELIX RANGEL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 98024-6617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arthur Rinaldi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/05/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO LUCAS BARRETO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 98797-5499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/08/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terça-feira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO HENRIQUE SANTANA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 97468-0042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIA SANTANA IRMÃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABRIEL BARBOSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTANIS LOURENÇO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 95648-5992</t>
   </si>
   <si>
     <t xml:space="preserve">São Paulo</t>
   </si>
   <si>
-    <t xml:space="preserve">Vanessa Mãe </t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/07/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:00 às 12:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EVERTON DA SILVA PAZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51 9697-9573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/10/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERICK CHRISTOFFER </t>
-  </si>
-  <si>
-    <t xml:space="preserve">51 9443-3883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/11/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHRISTIAN SILVA LOPES </t>
-  </si>
-  <si>
-    <t xml:space="preserve">51 982437559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/01/2026</t>
+    <t xml:space="preserve">Niveo Diegues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/04/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quarta-feira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LETÍCIA ALVES OLIVEIRA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 95475-3730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARINA AZEVEDO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 94165-0006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAVI ARENA LEAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 93357-4254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/08/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGO ARAUJO DOS SANTOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 98284-5882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/08/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMILA DO CARMO DOS SANTOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 98613-6502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juliana Lourenço Facci Rangel 29 anos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 99205-6396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/08/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LARISSA GERONIMO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 99190-3944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorocaba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARINA CARREGOSA RODRIGUES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 96209-7574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/01/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDRE ANDRE SANTOS CARVALHO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 99168-6105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIOVANE MATHEUS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEBORA OLIVEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 956609856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VICTOR HUGO LUCENA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 99388-4378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cecília Carvalho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guilherme de Figueiredo Rimola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 98805-8852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/06/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monique Lafond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO SUCUPIRA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 98624-7744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/11/2025</t>
   </si>
 </sst>
 </file>
@@ -234,7 +558,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -257,7 +580,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="Cambria"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -406,8 +728,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y25"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:Y46"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
@@ -433,7 +755,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="24" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -510,7 +832,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
@@ -527,10 +849,13 @@
         <v>29</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>30</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K2" s="0" t="s">
         <v>31</v>
@@ -545,208 +870,187 @@
         <v>31</v>
       </c>
       <c r="O2" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" s="0" t="s">
         <v>31</v>
       </c>
       <c r="Q2" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R2" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S2" s="0" t="s">
         <v>31</v>
       </c>
       <c r="T2" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U2" s="0" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X2" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S3" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T3" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="U3" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="X3" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y3" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J3" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q3" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="R3" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="S3" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="T3" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="U3" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="V3" s="2" t="n">
-        <v>380</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="X3" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="0" t="s">
-        <v>42</v>
-      </c>
+      <c r="B4" s="4"/>
       <c r="E4" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G4" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T4" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="U4" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="W4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="O4" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="P4" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q4" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="R4" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="S4" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="T4" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="U4" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>340</v>
-      </c>
-      <c r="W4" s="3" t="s">
+      <c r="X4" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="X4" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y4" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="Y4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4"/>
+      <c r="E5" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="G5" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>48</v>
-      </c>
       <c r="J5" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K5" s="0" t="s">
         <v>31</v>
@@ -761,63 +1065,50 @@
         <v>31</v>
       </c>
       <c r="O5" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P5" s="0" t="s">
         <v>31</v>
       </c>
       <c r="Q5" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R5" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S5" s="0" t="s">
         <v>31</v>
       </c>
       <c r="T5" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U5" s="0" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="X5" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y5" s="2" t="s">
-        <v>35</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="Y5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>42</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B6" s="4"/>
       <c r="E6" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="G6" s="0" t="s">
-        <v>53</v>
-      </c>
       <c r="J6" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K6" s="0" t="s">
         <v>31</v>
@@ -832,61 +1123,57 @@
         <v>31</v>
       </c>
       <c r="O6" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P6" s="0" t="s">
         <v>31</v>
       </c>
       <c r="Q6" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R6" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S6" s="0" t="s">
         <v>31</v>
       </c>
       <c r="T6" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U6" s="0" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>340</v>
-      </c>
-      <c r="W6" s="3" t="s">
-        <v>54</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="W6" s="4"/>
       <c r="X6" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y6" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="Y6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H7" s="2"/>
       <c r="J7" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K7" s="0" t="s">
         <v>31</v>
@@ -901,60 +1188,50 @@
         <v>31</v>
       </c>
       <c r="O7" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P7" s="0" t="s">
         <v>31</v>
       </c>
       <c r="Q7" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R7" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S7" s="0" t="s">
         <v>31</v>
       </c>
       <c r="T7" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U7" s="0" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="X7" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y7" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="Y7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>58</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B8" s="4"/>
       <c r="E8" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K8" s="0" t="s">
         <v>31</v>
@@ -963,166 +1240,2475 @@
         <v>31</v>
       </c>
       <c r="M8" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N8" s="0" t="s">
         <v>31</v>
       </c>
       <c r="O8" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P8" s="0" t="s">
         <v>31</v>
       </c>
       <c r="Q8" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R8" s="0" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S8" s="0" t="s">
         <v>31</v>
       </c>
       <c r="T8" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U8" s="0" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="X8" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="Y8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M9" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O9" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P9" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q9" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R9" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S9" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T9" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="U9" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="X9" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="E10" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J10" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M10" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="N10" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O10" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P10" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q10" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R10" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S10" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T10" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="U10" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="X10" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D11" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="E11" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J11" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M11" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="N11" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O11" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P11" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q11" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R11" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S11" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T11" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="U11" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="X11" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="E12" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="J12" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L12" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M12" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="N12" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O12" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P12" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q12" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R12" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S12" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T12" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="U12" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="X12" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="Y12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J13" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K13" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L13" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M13" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="N13" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O13" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P13" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q13" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R13" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S13" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T13" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="U13" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="W13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="X13" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="2" t="n">
+      <c r="Y13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="J14" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L14" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M14" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="N14" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O14" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P14" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q14" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R14" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S14" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T14" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="U14" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="X14" s="0" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J15" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L15" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M15" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="N15" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O15" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q15" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R15" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S15" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T15" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="U15" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="X15" s="0" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J16" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K16" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L16" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M16" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="N16" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O16" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P16" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q16" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R16" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S16" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T16" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="U16" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="W16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="X16" s="0" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J17" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K17" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L17" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M17" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="N17" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O17" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P17" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q17" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R17" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S17" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T17" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="U17" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="X17" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L18" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M18" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="N18" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O18" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="P18" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q18" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R18" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S18" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T18" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="U18" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="X18" s="0" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J19" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L19" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M19" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N19" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O19" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P19" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q19" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R19" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S19" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T19" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="U19" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="W19" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="X19" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J20" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K20" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L20" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M20" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N20" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O20" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P20" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q20" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R20" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S20" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T20" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="U20" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="X20" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K21" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L21" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M21" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N21" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O21" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P21" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q21" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R21" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S21" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T21" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="U21" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V21" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="X21" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J22" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K22" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L22" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M22" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O22" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P22" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q22" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R22" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S22" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T22" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="U22" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="X22" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J23" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K23" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L23" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M23" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N23" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O23" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P23" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q23" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R23" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S23" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T23" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="U23" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="X23" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="J24" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L24" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M24" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N24" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O24" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P24" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q24" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R24" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="S24" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T24" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="U24" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="X24" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="V9" s="2" t="n">
+      <c r="J25" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K25" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L25" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M25" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N25" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O25" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P25" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q25" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R25" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S25" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T25" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="U25" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V25" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="W25" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="X25" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J26" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K26" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L26" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M26" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N26" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O26" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P26" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q26" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R26" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S26" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T26" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="U26" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="X26" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J27" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K27" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L27" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M27" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N27" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O27" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P27" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q27" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R27" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S27" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T27" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="U27" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V27" s="0" t="n">
+        <v>260</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="X27" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J28" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K28" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L28" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M28" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N28" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O28" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P28" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q28" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R28" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S28" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T28" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="U28" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>340</v>
+      </c>
+      <c r="W28" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="X28" s="0" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G29" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="H29" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="J29" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K29" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L29" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M29" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N29" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O29" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P29" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q29" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R29" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S29" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T29" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="U29" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="X29" s="0" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="E30" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K30" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L30" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M30" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N30" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O30" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P30" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q30" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R30" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S30" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T30" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="U30" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="W30" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K31" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L31" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M31" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N31" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O31" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P31" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q31" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R31" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S31" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T31" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="U31" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V31" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="3"/>
-      <c r="Y10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="V11" s="2"/>
-      <c r="W11" s="3"/>
-      <c r="Y11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="V12" s="2"/>
-      <c r="W12" s="3"/>
-      <c r="Y12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="V13" s="2"/>
-      <c r="W13" s="3"/>
-      <c r="Y13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="F14" s="4"/>
-      <c r="H14" s="2"/>
-      <c r="V14" s="2"/>
-      <c r="W14" s="3"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="V15" s="2"/>
-      <c r="W15" s="3"/>
-    </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="F16" s="4"/>
-      <c r="V16" s="2"/>
-      <c r="W16" s="3"/>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="3"/>
-      <c r="Y17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="F18" s="4"/>
-      <c r="V18" s="2"/>
-      <c r="W18" s="3"/>
-    </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="3"/>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="3"/>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="3"/>
-    </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="W31" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="X31" s="0" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="D32" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="E32" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J32" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K32" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M32" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N32" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O32" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P32" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q32" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R32" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S32" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T32" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="U32" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="X32" s="0" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K33" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L33" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N33" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O33" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P33" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S33" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T33" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="U33" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="X33" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="D34" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="E34" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J34" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K34" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L34" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M34" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N34" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O34" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P34" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q34" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R34" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S34" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T34" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="U34" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="W34" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="X34" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="D35" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="E35" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K35" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L35" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M35" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N35" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O35" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P35" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q35" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R35" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S35" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T35" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="U35" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="X35" s="0" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="D36" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J36" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K36" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L36" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M36" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N36" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O36" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P36" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q36" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R36" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S36" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T36" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="U36" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V36" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="W36" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="X36" s="0" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="E37" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J37" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K37" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L37" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M37" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N37" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O37" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P37" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q37" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R37" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S37" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T37" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="U37" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V37" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="W37" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="X37" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C38" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="D38" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="E38" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J38" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K38" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L38" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M38" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N38" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O38" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P38" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q38" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R38" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S38" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T38" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="U38" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="W38" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="X38" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C39" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="D39" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="E39" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J39" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K39" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L39" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M39" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N39" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O39" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P39" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q39" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R39" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S39" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T39" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="U39" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V39" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="W39" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="X39" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C40" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="E40" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F40" s="4"/>
+      <c r="J40" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K40" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L40" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M40" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N40" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O40" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P40" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q40" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R40" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S40" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T40" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="U40" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="W40" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="X40" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B41" s="4"/>
+      <c r="C41" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="E41" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F41" s="4"/>
+      <c r="J41" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="K41" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L41" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M41" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N41" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O41" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P41" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q41" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R41" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S41" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T41" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="U41" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V41" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="X41" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="J42" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K42" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L42" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M42" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N42" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O42" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P42" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q42" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R42" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S42" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T42" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="U42" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V42" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="W42" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="X42" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F43" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="J43" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K43" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L43" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M43" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N43" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O43" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P43" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q43" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R43" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S43" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T43" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="U43" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V43" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="X43" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F44" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="J44" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K44" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L44" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M44" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N44" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O44" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P44" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q44" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R44" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S44" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T44" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="U44" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V44" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="X44" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E45" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F45" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="J45" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K45" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L45" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M45" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N45" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O45" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P45" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q45" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R45" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="S45" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="T45" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="U45" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V45" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="X45" s="0" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="E46" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F46" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J46" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="K46" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="L46" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="M46" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="N46" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O46" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="P46" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q46" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="R46" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="T46" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="U46" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="V46" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="X46" s="0" t="s">
+        <v>134</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/exemplo_importacao_alunos.xlsx
+++ b/exemplo_importacao_alunos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="193">
   <si>
     <t xml:space="preserve">nome</t>
   </si>
@@ -148,7 +148,16 @@
     <t xml:space="preserve">29/03/2025</t>
   </si>
   <si>
-    <t xml:space="preserve">PERIC</t>
+    <t xml:space="preserve">Gabriel PERIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 96074-0877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">São Paulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP</t>
   </si>
   <si>
     <t xml:space="preserve">03/04/2025</t>
@@ -157,18 +166,39 @@
     <t xml:space="preserve">Quinta-feira</t>
   </si>
   <si>
+    <t xml:space="preserve">19:00 às 21:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">Matheus Moreski</t>
   </si>
   <si>
+    <t xml:space="preserve">65 9356-2063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MT</t>
+  </si>
+  <si>
     <t xml:space="preserve">mãe Fernanda </t>
   </si>
   <si>
     <t xml:space="preserve">MARK</t>
   </si>
   <si>
+    <t xml:space="preserve">21 99929-0869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rio de Janeiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RJ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sábado</t>
   </si>
   <si>
+    <t xml:space="preserve">10:00 às 12:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">ERICK JENUINO DEBIAZI</t>
   </si>
   <si>
@@ -184,6 +214,12 @@
     <t xml:space="preserve">BRUNA AUEBACH</t>
   </si>
   <si>
+    <t xml:space="preserve">47 9763-5094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC</t>
+  </si>
+  <si>
     <t xml:space="preserve">03/07/2025</t>
   </si>
   <si>
@@ -202,6 +238,9 @@
     <t xml:space="preserve">Jacqueline Mendes Magalhães</t>
   </si>
   <si>
+    <t xml:space="preserve">21 99367-1641</t>
+  </si>
+  <si>
     <t xml:space="preserve">18/07/2025</t>
   </si>
   <si>
@@ -211,18 +250,21 @@
     <t xml:space="preserve">21 98986-1122</t>
   </si>
   <si>
-    <t xml:space="preserve">Rio de Janeiro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RJ</t>
-  </si>
-  <si>
     <t xml:space="preserve">20/09/2025</t>
   </si>
   <si>
     <t xml:space="preserve">GABRIEL SANCHES SERQUEIRA</t>
   </si>
   <si>
+    <t xml:space="preserve">61 433 429 513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brasília</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DF</t>
+  </si>
+  <si>
     <t xml:space="preserve">20/08/2025</t>
   </si>
   <si>
@@ -241,9 +283,6 @@
     <t xml:space="preserve">19 98170-3566</t>
   </si>
   <si>
-    <t xml:space="preserve">SP</t>
-  </si>
-  <si>
     <t xml:space="preserve">01/10/2025</t>
   </si>
   <si>
@@ -253,9 +292,6 @@
     <t xml:space="preserve">47 9707-5558</t>
   </si>
   <si>
-    <t xml:space="preserve">SC</t>
-  </si>
-  <si>
     <t xml:space="preserve">17/10/2025</t>
   </si>
   <si>
@@ -307,6 +343,9 @@
     <t xml:space="preserve">31/05/2025</t>
   </si>
   <si>
+    <t xml:space="preserve">10:30 às 12:30</t>
+  </si>
+  <si>
     <t xml:space="preserve">PAULO ROBERTO SANTOS DA SILVA</t>
   </si>
   <si>
@@ -343,7 +382,7 @@
     <t xml:space="preserve">25/09/2025</t>
   </si>
   <si>
-    <t xml:space="preserve">EXPERIMENTAL Gabriella dos Santos</t>
+    <t xml:space="preserve">Gabriella dos Santos</t>
   </si>
   <si>
     <t xml:space="preserve">00000-0000</t>
@@ -382,6 +421,9 @@
     <t xml:space="preserve">17/05/2025</t>
   </si>
   <si>
+    <t xml:space="preserve">09:00 às 11:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">PEDRO LUCAS BARRETO </t>
   </si>
   <si>
@@ -415,9 +457,6 @@
     <t xml:space="preserve">11 95648-5992</t>
   </si>
   <si>
-    <t xml:space="preserve">São Paulo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Niveo Diegues</t>
   </si>
   <si>
@@ -427,6 +466,9 @@
     <t xml:space="preserve">Quarta-feira</t>
   </si>
   <si>
+    <t xml:space="preserve">19:30 às 22:30</t>
+  </si>
+  <si>
     <t xml:space="preserve">LETÍCIA ALVES OLIVEIRA </t>
   </si>
   <si>
@@ -445,6 +487,9 @@
     <t xml:space="preserve">26/07/2025</t>
   </si>
   <si>
+    <t xml:space="preserve">09:30 às 11:30</t>
+  </si>
+  <si>
     <t xml:space="preserve">DAVI ARENA LEAL</t>
   </si>
   <si>
@@ -478,6 +523,9 @@
     <t xml:space="preserve">27/08/2025</t>
   </si>
   <si>
+    <t xml:space="preserve">15:00 às 18:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">LARISSA GERONIMO</t>
   </si>
   <si>
@@ -487,6 +535,9 @@
     <t xml:space="preserve">Sorocaba</t>
   </si>
   <si>
+    <t xml:space="preserve">10:00 às 13:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">MARINA CARREGOSA RODRIGUES</t>
   </si>
   <si>
@@ -520,6 +571,9 @@
     <t xml:space="preserve">Cecília Carvalho</t>
   </si>
   <si>
+    <t xml:space="preserve">14:30 às 16:30</t>
+  </si>
+  <si>
     <t xml:space="preserve">Guilherme de Figueiredo Rimola</t>
   </si>
   <si>
@@ -533,6 +587,9 @@
   </si>
   <si>
     <t xml:space="preserve">20/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:00 às 20:00</t>
   </si>
   <si>
     <t xml:space="preserve">PEDRO SUCUPIRA </t>
@@ -558,6 +615,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -580,6 +638,7 @@
       <color rgb="FFFFFFFF"/>
       <name val="Cambria"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -981,7 +1040,15 @@
       <c r="A4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="4"/>
+      <c r="B4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>45</v>
+      </c>
       <c r="E4" s="0" t="s">
         <v>29</v>
       </c>
@@ -995,7 +1062,7 @@
         <v>31</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M4" s="0" t="s">
         <v>31</v>
@@ -1004,7 +1071,7 @@
         <v>31</v>
       </c>
       <c r="O4" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P4" s="0" t="s">
         <v>31</v>
@@ -1022,24 +1089,34 @@
         <v>33</v>
       </c>
       <c r="U4" s="0" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V4" s="2" t="n">
         <v>300</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="X4" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y4" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>51</v>
+      </c>
       <c r="E5" s="0" t="s">
         <v>29</v>
       </c>
@@ -1047,7 +1124,7 @@
         <v>5</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J5" s="0" t="s">
         <v>31</v>
@@ -1056,7 +1133,7 @@
         <v>31</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M5" s="0" t="s">
         <v>31</v>
@@ -1065,7 +1142,7 @@
         <v>31</v>
       </c>
       <c r="O5" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P5" s="0" t="s">
         <v>31</v>
@@ -1083,24 +1160,34 @@
         <v>33</v>
       </c>
       <c r="U5" s="0" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V5" s="2" t="n">
         <v>300</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="X5" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y5" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="4"/>
+        <v>53</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>56</v>
+      </c>
       <c r="E6" s="0" t="s">
         <v>29</v>
       </c>
@@ -1114,7 +1201,7 @@
         <v>31</v>
       </c>
       <c r="L6" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M6" s="0" t="s">
         <v>31</v>
@@ -1123,7 +1210,7 @@
         <v>31</v>
       </c>
       <c r="O6" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P6" s="0" t="s">
         <v>31</v>
@@ -1148,22 +1235,24 @@
       </c>
       <c r="W6" s="4"/>
       <c r="X6" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y6" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>29</v>
@@ -1179,7 +1268,7 @@
         <v>31</v>
       </c>
       <c r="L7" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M7" s="0" t="s">
         <v>31</v>
@@ -1188,7 +1277,7 @@
         <v>31</v>
       </c>
       <c r="O7" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P7" s="0" t="s">
         <v>31</v>
@@ -1206,24 +1295,34 @@
         <v>33</v>
       </c>
       <c r="U7" s="0" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V7" s="2" t="n">
         <v>350</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="X7" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y7" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="4"/>
+        <v>63</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>65</v>
+      </c>
       <c r="E8" s="0" t="s">
         <v>29</v>
       </c>
@@ -1237,16 +1336,16 @@
         <v>31</v>
       </c>
       <c r="L8" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M8" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N8" s="0" t="s">
         <v>31</v>
       </c>
       <c r="O8" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P8" s="0" t="s">
         <v>31</v>
@@ -1264,25 +1363,27 @@
         <v>33</v>
       </c>
       <c r="U8" s="0" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V8" s="2" t="n">
         <v>300</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="X8" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y8" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>28</v>
@@ -1306,7 +1407,7 @@
         <v>31</v>
       </c>
       <c r="M9" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N9" s="0" t="s">
         <v>31</v>
@@ -1330,24 +1431,34 @@
         <v>33</v>
       </c>
       <c r="U9" s="0" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V9" s="2" t="n">
         <v>280</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="X9" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>70</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="4"/>
+        <v>71</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>56</v>
+      </c>
       <c r="E10" s="0" t="s">
         <v>29</v>
       </c>
@@ -1394,25 +1505,27 @@
         <v>300</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="X10" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y10" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>29</v>
@@ -1427,7 +1540,7 @@
         <v>31</v>
       </c>
       <c r="L11" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M11" s="0" t="s">
         <v>31</v>
@@ -1436,7 +1549,7 @@
         <v>31</v>
       </c>
       <c r="O11" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P11" s="0" t="s">
         <v>31</v>
@@ -1460,18 +1573,28 @@
         <v>260</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="X11" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>57</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="4"/>
+        <v>77</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>80</v>
+      </c>
       <c r="E12" s="0" t="s">
         <v>29</v>
       </c>
@@ -1486,7 +1609,7 @@
         <v>31</v>
       </c>
       <c r="L12" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M12" s="0" t="s">
         <v>31</v>
@@ -1495,7 +1618,7 @@
         <v>31</v>
       </c>
       <c r="O12" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P12" s="0" t="s">
         <v>31</v>
@@ -1513,31 +1636,33 @@
         <v>33</v>
       </c>
       <c r="U12" s="0" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V12" s="2" t="n">
         <v>300</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="X12" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>70</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E13" s="0" t="s">
         <v>29</v>
@@ -1552,7 +1677,7 @@
         <v>31</v>
       </c>
       <c r="L13" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M13" s="0" t="s">
         <v>31</v>
@@ -1561,7 +1686,7 @@
         <v>31</v>
       </c>
       <c r="O13" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P13" s="0" t="s">
         <v>31</v>
@@ -1579,31 +1704,33 @@
         <v>33</v>
       </c>
       <c r="U13" s="0" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V13" s="2" t="n">
         <v>260</v>
       </c>
       <c r="W13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="X13" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="X13" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y13" s="2"/>
+      <c r="Y13" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>29</v>
@@ -1619,7 +1746,7 @@
         <v>31</v>
       </c>
       <c r="L14" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M14" s="0" t="s">
         <v>31</v>
@@ -1628,7 +1755,7 @@
         <v>31</v>
       </c>
       <c r="O14" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P14" s="0" t="s">
         <v>31</v>
@@ -1637,7 +1764,7 @@
         <v>32</v>
       </c>
       <c r="R14" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S14" s="0" t="s">
         <v>31</v>
@@ -1646,30 +1773,33 @@
         <v>33</v>
       </c>
       <c r="U14" s="0" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V14" s="2" t="n">
         <v>340</v>
       </c>
       <c r="W14" s="3" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="X14" s="0" t="s">
-        <v>58</v>
+        <v>70</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E15" s="0" t="s">
         <v>29</v>
@@ -1684,7 +1814,7 @@
         <v>31</v>
       </c>
       <c r="L15" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M15" s="0" t="s">
         <v>31</v>
@@ -1693,7 +1823,7 @@
         <v>31</v>
       </c>
       <c r="O15" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P15" s="0" t="s">
         <v>31</v>
@@ -1711,30 +1841,33 @@
         <v>33</v>
       </c>
       <c r="U15" s="0" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V15" s="2" t="n">
         <v>340</v>
       </c>
       <c r="W15" s="3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="X15" s="0" t="s">
-        <v>58</v>
+        <v>70</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E16" s="0" t="s">
         <v>29</v>
@@ -1749,7 +1882,7 @@
         <v>31</v>
       </c>
       <c r="L16" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M16" s="0" t="s">
         <v>31</v>
@@ -1758,7 +1891,7 @@
         <v>31</v>
       </c>
       <c r="O16" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P16" s="0" t="s">
         <v>31</v>
@@ -1776,30 +1909,33 @@
         <v>33</v>
       </c>
       <c r="U16" s="0" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V16" s="2" t="n">
         <v>300</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="X16" s="0" t="s">
-        <v>58</v>
+        <v>70</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E17" s="0" t="s">
         <v>29</v>
@@ -1814,7 +1950,7 @@
         <v>31</v>
       </c>
       <c r="L17" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M17" s="0" t="s">
         <v>31</v>
@@ -1823,7 +1959,7 @@
         <v>31</v>
       </c>
       <c r="O17" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P17" s="0" t="s">
         <v>31</v>
@@ -1832,7 +1968,7 @@
         <v>32</v>
       </c>
       <c r="R17" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S17" s="0" t="s">
         <v>31</v>
@@ -1841,31 +1977,33 @@
         <v>33</v>
       </c>
       <c r="U17" s="0" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V17" s="2" t="n">
         <v>300</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="X17" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>47</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="E18" s="0" t="s">
         <v>29</v>
@@ -1880,7 +2018,7 @@
         <v>31</v>
       </c>
       <c r="L18" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M18" s="0" t="s">
         <v>31</v>
@@ -1889,7 +2027,7 @@
         <v>31</v>
       </c>
       <c r="O18" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P18" s="0" t="s">
         <v>31</v>
@@ -1907,30 +2045,33 @@
         <v>33</v>
       </c>
       <c r="U18" s="0" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V18" s="2" t="n">
         <v>280</v>
       </c>
       <c r="W18" s="3" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="X18" s="0" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>47</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E19" s="0" t="s">
         <v>29</v>
@@ -1969,7 +2110,7 @@
         <v>31</v>
       </c>
       <c r="T19" s="0" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="U19" s="0" t="s">
         <v>12</v>
@@ -1978,24 +2119,27 @@
         <v>360</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="X19" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="Y19" s="0" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E20" s="0" t="s">
         <v>29</v>
@@ -2034,7 +2178,7 @@
         <v>31</v>
       </c>
       <c r="T20" s="0" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="U20" s="0" t="s">
         <v>12</v>
@@ -2043,24 +2187,27 @@
         <v>260</v>
       </c>
       <c r="W20" s="3" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="X20" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="Y20" s="0" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E21" s="0" t="s">
         <v>29</v>
@@ -2099,7 +2246,7 @@
         <v>31</v>
       </c>
       <c r="T21" s="0" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="U21" s="0" t="s">
         <v>12</v>
@@ -2108,24 +2255,27 @@
         <v>280</v>
       </c>
       <c r="W21" s="3" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="X21" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="Y21" s="0" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E22" s="0" t="s">
         <v>29</v>
@@ -2164,7 +2314,7 @@
         <v>31</v>
       </c>
       <c r="T22" s="0" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="U22" s="0" t="s">
         <v>12</v>
@@ -2173,24 +2323,27 @@
         <v>280</v>
       </c>
       <c r="W22" s="3" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="X22" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="Y22" s="0" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E23" s="0" t="s">
         <v>29</v>
@@ -2229,7 +2382,7 @@
         <v>31</v>
       </c>
       <c r="T23" s="0" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="U23" s="0" t="s">
         <v>12</v>
@@ -2238,18 +2391,21 @@
         <v>300</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="X23" s="0" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>57</v>
+      </c>
+      <c r="Y23" s="0" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="E24" s="0" t="s">
         <v>29</v>
@@ -2286,7 +2442,7 @@
         <v>32</v>
       </c>
       <c r="T24" s="0" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="U24" s="0" t="s">
         <v>12</v>
@@ -2295,24 +2451,27 @@
         <v>60</v>
       </c>
       <c r="W24" s="3" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="X24" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="Y24" s="0" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E25" s="0" t="s">
         <v>29</v>
@@ -2351,7 +2510,7 @@
         <v>31</v>
       </c>
       <c r="T25" s="0" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="U25" s="0" t="s">
         <v>12</v>
@@ -2360,24 +2519,27 @@
         <v>280</v>
       </c>
       <c r="W25" s="3" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="X25" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="Y25" s="0" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E26" s="0" t="s">
         <v>29</v>
@@ -2416,7 +2578,7 @@
         <v>31</v>
       </c>
       <c r="T26" s="0" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="U26" s="0" t="s">
         <v>12</v>
@@ -2425,24 +2587,27 @@
         <v>280</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="X26" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="Y26" s="0" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E27" s="0" t="s">
         <v>29</v>
@@ -2481,7 +2646,7 @@
         <v>31</v>
       </c>
       <c r="T27" s="0" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="U27" s="0" t="s">
         <v>12</v>
@@ -2490,24 +2655,27 @@
         <v>260</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="X27" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="Y27" s="0" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E28" s="0" t="s">
         <v>29</v>
@@ -2546,7 +2714,7 @@
         <v>31</v>
       </c>
       <c r="T28" s="0" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="U28" s="0" t="s">
         <v>12</v>
@@ -2555,24 +2723,27 @@
         <v>340</v>
       </c>
       <c r="W28" s="3" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="X28" s="0" t="s">
-        <v>123</v>
+        <v>137</v>
+      </c>
+      <c r="Y28" s="0" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E29" s="0" t="s">
         <v>29</v>
@@ -2581,10 +2752,10 @@
         <v>15</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="J29" s="0" t="s">
         <v>31</v>
@@ -2617,7 +2788,7 @@
         <v>31</v>
       </c>
       <c r="T29" s="0" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="U29" s="0" t="s">
         <v>12</v>
@@ -2626,15 +2797,18 @@
         <v>600</v>
       </c>
       <c r="W29" s="3" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="X29" s="0" t="s">
-        <v>123</v>
+        <v>137</v>
+      </c>
+      <c r="Y29" s="0" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="B30" s="4"/>
       <c r="E30" s="0" t="s">
@@ -2674,7 +2848,7 @@
         <v>31</v>
       </c>
       <c r="T30" s="0" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="U30" s="0" t="s">
         <v>12</v>
@@ -2683,21 +2857,21 @@
         <v>290</v>
       </c>
       <c r="W30" s="3" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E31" s="0" t="s">
         <v>29</v>
@@ -2736,7 +2910,7 @@
         <v>31</v>
       </c>
       <c r="T31" s="0" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="U31" s="0" t="s">
         <v>12</v>
@@ -2745,24 +2919,27 @@
         <v>360</v>
       </c>
       <c r="W31" s="3" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="X31" s="0" t="s">
-        <v>134</v>
+        <v>147</v>
+      </c>
+      <c r="Y31" s="0" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E32" s="0" t="s">
         <v>29</v>
@@ -2801,7 +2978,7 @@
         <v>31</v>
       </c>
       <c r="T32" s="0" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="U32" s="0" t="s">
         <v>12</v>
@@ -2810,24 +2987,27 @@
         <v>360</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="X32" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="Y32" s="0" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E33" s="0" t="s">
         <v>29</v>
@@ -2866,7 +3046,7 @@
         <v>31</v>
       </c>
       <c r="T33" s="0" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="U33" s="0" t="s">
         <v>12</v>
@@ -2875,24 +3055,27 @@
         <v>400</v>
       </c>
       <c r="W33" s="3" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="X33" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="Y33" s="0" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E34" s="0" t="s">
         <v>29</v>
@@ -2931,7 +3114,7 @@
         <v>31</v>
       </c>
       <c r="T34" s="0" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="U34" s="0" t="s">
         <v>12</v>
@@ -2940,24 +3123,27 @@
         <v>360</v>
       </c>
       <c r="W34" s="3" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="X34" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="Y34" s="0" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E35" s="0" t="s">
         <v>29</v>
@@ -2996,7 +3182,7 @@
         <v>31</v>
       </c>
       <c r="T35" s="0" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="U35" s="0" t="s">
         <v>12</v>
@@ -3005,24 +3191,27 @@
         <v>380</v>
       </c>
       <c r="W35" s="3" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="X35" s="0" t="s">
-        <v>134</v>
+        <v>147</v>
+      </c>
+      <c r="Y35" s="0" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E36" s="0" t="s">
         <v>29</v>
@@ -3061,7 +3250,7 @@
         <v>31</v>
       </c>
       <c r="T36" s="0" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="U36" s="0" t="s">
         <v>12</v>
@@ -3070,24 +3259,27 @@
         <v>400</v>
       </c>
       <c r="W36" s="3" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="X36" s="0" t="s">
-        <v>134</v>
+        <v>147</v>
+      </c>
+      <c r="Y36" s="0" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E37" s="0" t="s">
         <v>29</v>
@@ -3126,7 +3318,7 @@
         <v>31</v>
       </c>
       <c r="T37" s="0" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="U37" s="0" t="s">
         <v>12</v>
@@ -3135,24 +3327,27 @@
         <v>400</v>
       </c>
       <c r="W37" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="X37" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="Y37" s="0" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E38" s="0" t="s">
         <v>29</v>
@@ -3191,7 +3386,7 @@
         <v>31</v>
       </c>
       <c r="T38" s="0" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="U38" s="0" t="s">
         <v>12</v>
@@ -3200,24 +3395,27 @@
         <v>310</v>
       </c>
       <c r="W38" s="3" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="X38" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="Y38" s="0" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E39" s="0" t="s">
         <v>29</v>
@@ -3256,7 +3454,7 @@
         <v>31</v>
       </c>
       <c r="T39" s="0" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="U39" s="0" t="s">
         <v>12</v>
@@ -3265,24 +3463,27 @@
         <v>360</v>
       </c>
       <c r="W39" s="3" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="X39" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="Y39" s="0" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E40" s="0" t="s">
         <v>29</v>
@@ -3319,7 +3520,7 @@
         <v>31</v>
       </c>
       <c r="T40" s="0" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="U40" s="0" t="s">
         <v>12</v>
@@ -3328,22 +3529,25 @@
         <v>360</v>
       </c>
       <c r="W40" s="3" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="X40" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="Y40" s="0" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="0" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E41" s="0" t="s">
         <v>29</v>
@@ -3380,7 +3584,7 @@
         <v>31</v>
       </c>
       <c r="T41" s="0" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="U41" s="0" t="s">
         <v>12</v>
@@ -3389,24 +3593,24 @@
         <v>380</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="X41" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E42" s="0" t="s">
         <v>29</v>
@@ -3442,7 +3646,7 @@
         <v>31</v>
       </c>
       <c r="T42" s="0" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="U42" s="0" t="s">
         <v>12</v>
@@ -3451,24 +3655,27 @@
         <v>400</v>
       </c>
       <c r="W42" s="3" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="X42" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="Y42" s="0" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E43" s="0" t="s">
         <v>29</v>
@@ -3507,7 +3714,7 @@
         <v>31</v>
       </c>
       <c r="T43" s="0" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="U43" s="0" t="s">
         <v>12</v>
@@ -3516,21 +3723,24 @@
         <v>280</v>
       </c>
       <c r="X43" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="Y43" s="0" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E44" s="0" t="s">
         <v>29</v>
@@ -3569,7 +3779,7 @@
         <v>31</v>
       </c>
       <c r="T44" s="0" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="U44" s="0" t="s">
         <v>12</v>
@@ -3578,22 +3788,27 @@
         <v>350</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="X44" s="0" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="Y44" s="0" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B45" s="4"/>
+        <v>74</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>75</v>
+      </c>
       <c r="C45" s="0" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E45" s="0" t="s">
         <v>29</v>
@@ -3632,7 +3847,7 @@
         <v>31</v>
       </c>
       <c r="T45" s="0" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="U45" s="0" t="s">
         <v>12</v>
@@ -3641,24 +3856,27 @@
         <v>300</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="X45" s="0" t="s">
-        <v>134</v>
+        <v>147</v>
+      </c>
+      <c r="Y45" s="0" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E46" s="0" t="s">
         <v>29</v>
@@ -3693,8 +3911,11 @@
       <c r="R46" s="0" t="s">
         <v>32</v>
       </c>
+      <c r="S46" s="0" t="s">
+        <v>31</v>
+      </c>
       <c r="T46" s="0" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="U46" s="0" t="s">
         <v>12</v>
@@ -3703,10 +3924,13 @@
         <v>300</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="X46" s="0" t="s">
-        <v>134</v>
+        <v>147</v>
+      </c>
+      <c r="Y46" s="0" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/exemplo_importacao_alunos.xlsx
+++ b/exemplo_importacao_alunos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="198">
   <si>
     <t xml:space="preserve">nome</t>
   </si>
@@ -385,7 +385,10 @@
     <t xml:space="preserve">Gabriella dos Santos</t>
   </si>
   <si>
-    <t xml:space="preserve">00000-0000</t>
+    <t xml:space="preserve">99 12345-6789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N/A</t>
   </si>
   <si>
     <t xml:space="preserve">01/11/2025</t>
@@ -451,6 +454,9 @@
     <t xml:space="preserve">GABRIEL BARBOSA</t>
   </si>
   <si>
+    <t xml:space="preserve">21 97121-1726</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALTANIS LOURENÇO </t>
   </si>
   <si>
@@ -554,6 +560,15 @@
   </si>
   <si>
     <t xml:space="preserve">GIOVANE MATHEUS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 98556-1166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanessa Mãe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 99231-6969</t>
   </si>
   <si>
     <t xml:space="preserve">DEBORA OLIVEIRA DA SILVA</t>
@@ -2407,6 +2422,12 @@
       <c r="B24" s="2" t="s">
         <v>121</v>
       </c>
+      <c r="C24" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>122</v>
+      </c>
       <c r="E24" s="0" t="s">
         <v>29</v>
       </c>
@@ -2451,7 +2472,7 @@
         <v>60</v>
       </c>
       <c r="W24" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="X24" s="0" t="s">
         <v>57</v>
@@ -2462,10 +2483,10 @@
     </row>
     <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>55</v>
@@ -2519,7 +2540,7 @@
         <v>280</v>
       </c>
       <c r="W25" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="X25" s="0" t="s">
         <v>57</v>
@@ -2530,10 +2551,10 @@
     </row>
     <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>55</v>
@@ -2587,7 +2608,7 @@
         <v>280</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="X26" s="0" t="s">
         <v>57</v>
@@ -2598,10 +2619,10 @@
     </row>
     <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>55</v>
@@ -2646,7 +2667,7 @@
         <v>31</v>
       </c>
       <c r="T27" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="U27" s="0" t="s">
         <v>12</v>
@@ -2655,21 +2676,21 @@
         <v>260</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="X27" s="0" t="s">
         <v>57</v>
       </c>
       <c r="Y27" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>55</v>
@@ -2714,7 +2735,7 @@
         <v>31</v>
       </c>
       <c r="T28" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="U28" s="0" t="s">
         <v>12</v>
@@ -2723,10 +2744,10 @@
         <v>340</v>
       </c>
       <c r="W28" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="X28" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Y28" s="0" t="s">
         <v>48</v>
@@ -2734,10 +2755,10 @@
     </row>
     <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>55</v>
@@ -2752,11 +2773,11 @@
         <v>15</v>
       </c>
       <c r="G29" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="H29" s="0" t="s">
         <v>140</v>
       </c>
-      <c r="H29" s="0" t="s">
-        <v>139</v>
-      </c>
       <c r="J29" s="0" t="s">
         <v>31</v>
       </c>
@@ -2788,7 +2809,7 @@
         <v>31</v>
       </c>
       <c r="T29" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="U29" s="0" t="s">
         <v>12</v>
@@ -2797,10 +2818,10 @@
         <v>600</v>
       </c>
       <c r="W29" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="X29" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Y29" s="0" t="s">
         <v>48</v>
@@ -2808,9 +2829,17 @@
     </row>
     <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B30" s="4"/>
+        <v>143</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>56</v>
+      </c>
       <c r="E30" s="0" t="s">
         <v>29</v>
       </c>
@@ -2848,7 +2877,7 @@
         <v>31</v>
       </c>
       <c r="T30" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="U30" s="0" t="s">
         <v>12</v>
@@ -2857,15 +2886,15 @@
         <v>290</v>
       </c>
       <c r="W30" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>44</v>
@@ -2910,7 +2939,7 @@
         <v>31</v>
       </c>
       <c r="T31" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="U31" s="0" t="s">
         <v>12</v>
@@ -2919,21 +2948,21 @@
         <v>360</v>
       </c>
       <c r="W31" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="X31" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Y31" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>44</v>
@@ -2978,7 +3007,7 @@
         <v>31</v>
       </c>
       <c r="T32" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="U32" s="0" t="s">
         <v>12</v>
@@ -2987,21 +3016,21 @@
         <v>360</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="X32" s="0" t="s">
         <v>47</v>
       </c>
       <c r="Y32" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>44</v>
@@ -3046,7 +3075,7 @@
         <v>31</v>
       </c>
       <c r="T33" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="U33" s="0" t="s">
         <v>12</v>
@@ -3055,21 +3084,21 @@
         <v>400</v>
       </c>
       <c r="W33" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="X33" s="0" t="s">
         <v>57</v>
       </c>
       <c r="Y33" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>44</v>
@@ -3114,7 +3143,7 @@
         <v>31</v>
       </c>
       <c r="T34" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="U34" s="0" t="s">
         <v>12</v>
@@ -3123,21 +3152,21 @@
         <v>360</v>
       </c>
       <c r="W34" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="X34" s="0" t="s">
         <v>57</v>
       </c>
       <c r="Y34" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>44</v>
@@ -3182,7 +3211,7 @@
         <v>31</v>
       </c>
       <c r="T35" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="U35" s="0" t="s">
         <v>12</v>
@@ -3191,21 +3220,21 @@
         <v>380</v>
       </c>
       <c r="W35" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="X35" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Y35" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>44</v>
@@ -3250,7 +3279,7 @@
         <v>31</v>
       </c>
       <c r="T36" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="U36" s="0" t="s">
         <v>12</v>
@@ -3262,18 +3291,18 @@
         <v>69</v>
       </c>
       <c r="X36" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Y36" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>44</v>
@@ -3318,7 +3347,7 @@
         <v>31</v>
       </c>
       <c r="T37" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="U37" s="0" t="s">
         <v>12</v>
@@ -3327,24 +3356,24 @@
         <v>400</v>
       </c>
       <c r="W37" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="X37" s="0" t="s">
         <v>57</v>
       </c>
       <c r="Y37" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>45</v>
@@ -3386,7 +3415,7 @@
         <v>31</v>
       </c>
       <c r="T38" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="U38" s="0" t="s">
         <v>12</v>
@@ -3395,21 +3424,21 @@
         <v>310</v>
       </c>
       <c r="W38" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="X38" s="0" t="s">
         <v>57</v>
       </c>
       <c r="Y38" s="0" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>44</v>
@@ -3454,7 +3483,7 @@
         <v>31</v>
       </c>
       <c r="T39" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="U39" s="0" t="s">
         <v>12</v>
@@ -3463,21 +3492,21 @@
         <v>360</v>
       </c>
       <c r="W39" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="X39" s="0" t="s">
         <v>57</v>
       </c>
       <c r="Y39" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>44</v>
@@ -3520,7 +3549,7 @@
         <v>31</v>
       </c>
       <c r="T40" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="U40" s="0" t="s">
         <v>12</v>
@@ -3529,20 +3558,22 @@
         <v>360</v>
       </c>
       <c r="W40" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="X40" s="0" t="s">
         <v>57</v>
       </c>
       <c r="Y40" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B41" s="4"/>
+        <v>179</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>180</v>
+      </c>
       <c r="C41" s="0" t="s">
         <v>44</v>
       </c>
@@ -3553,6 +3584,12 @@
         <v>29</v>
       </c>
       <c r="F41" s="4"/>
+      <c r="G41" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="H41" s="0" t="s">
+        <v>182</v>
+      </c>
       <c r="J41" s="0" t="s">
         <v>32</v>
       </c>
@@ -3584,7 +3621,7 @@
         <v>31</v>
       </c>
       <c r="T41" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="U41" s="0" t="s">
         <v>12</v>
@@ -3593,7 +3630,7 @@
         <v>380</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="X41" s="0" t="s">
         <v>57</v>
@@ -3601,10 +3638,10 @@
     </row>
     <row r="42" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C42" s="0" t="s">
         <v>44</v>
@@ -3646,7 +3683,7 @@
         <v>31</v>
       </c>
       <c r="T42" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="U42" s="0" t="s">
         <v>12</v>
@@ -3655,21 +3692,21 @@
         <v>400</v>
       </c>
       <c r="W42" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="X42" s="0" t="s">
         <v>57</v>
       </c>
       <c r="Y42" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C43" s="0" t="s">
         <v>55</v>
@@ -3714,7 +3751,7 @@
         <v>31</v>
       </c>
       <c r="T43" s="0" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="U43" s="0" t="s">
         <v>12</v>
@@ -3726,15 +3763,15 @@
         <v>57</v>
       </c>
       <c r="Y43" s="0" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C44" s="0" t="s">
         <v>55</v>
@@ -3779,7 +3816,7 @@
         <v>31</v>
       </c>
       <c r="T44" s="0" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="U44" s="0" t="s">
         <v>12</v>
@@ -3788,13 +3825,13 @@
         <v>350</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="X44" s="0" t="s">
         <v>57</v>
       </c>
       <c r="Y44" s="0" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3847,7 +3884,7 @@
         <v>31</v>
       </c>
       <c r="T45" s="0" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="U45" s="0" t="s">
         <v>12</v>
@@ -3856,21 +3893,21 @@
         <v>300</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="X45" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Y45" s="0" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C46" s="0" t="s">
         <v>55</v>
@@ -3915,7 +3952,7 @@
         <v>31</v>
       </c>
       <c r="T46" s="0" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="U46" s="0" t="s">
         <v>12</v>
@@ -3924,13 +3961,13 @@
         <v>300</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="X46" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Y46" s="0" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
